--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260919_215251.xlsx
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
